--- a/model/Output_Budget/1. Baseline/Summary.xlsx
+++ b/model/Output_Budget/1. Baseline/Summary.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/Model-1/model/Output_Budget/1. Baseline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_DC4DAA97EFA9C6E015EA8A82C0890603104BC42E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61942DD6-7753-49C0-9052-0DB53885100B}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_B9E4ED474AC174C29323803AD60FB83079127B7E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3B3F551-4818-4936-9570-126E156CD1A2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="250000" sheetId="1" r:id="rId1"/>
-    <sheet name="400000" sheetId="9" r:id="rId2"/>
-    <sheet name="750000" sheetId="3" r:id="rId3"/>
-    <sheet name="1000000" sheetId="4" r:id="rId4"/>
-    <sheet name="1250000" sheetId="5" r:id="rId5"/>
-    <sheet name="1500000" sheetId="6" r:id="rId6"/>
-    <sheet name="1750000" sheetId="7" r:id="rId7"/>
-    <sheet name="2000000" sheetId="8" r:id="rId8"/>
+    <sheet name="100000" sheetId="10" r:id="rId1"/>
+    <sheet name="250000" sheetId="1" r:id="rId2"/>
+    <sheet name="400000" sheetId="9" r:id="rId3"/>
+    <sheet name="750000" sheetId="3" r:id="rId4"/>
+    <sheet name="1000000" sheetId="4" r:id="rId5"/>
+    <sheet name="1250000" sheetId="5" r:id="rId6"/>
+    <sheet name="1500000" sheetId="6" r:id="rId7"/>
+    <sheet name="1750000" sheetId="7" r:id="rId8"/>
+    <sheet name="2000000" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="4">
   <si>
     <t>Prices</t>
   </si>
@@ -401,11 +402,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:AU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
         <v>0</v>
       </c>
@@ -529,8 +530,23 @@
       <c r="AP1" s="1">
         <v>40</v>
       </c>
+      <c r="AQ1" s="1">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="1">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="1">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="1">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="1">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,8 +673,23 @@
       <c r="AP2">
         <v>0.4</v>
       </c>
+      <c r="AQ2">
+        <v>0.41</v>
+      </c>
+      <c r="AR2">
+        <v>0.42</v>
+      </c>
+      <c r="AS2">
+        <v>0.43</v>
+      </c>
+      <c r="AT2">
+        <v>0.44</v>
+      </c>
+      <c r="AU2">
+        <v>0.45</v>
+      </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -756,37 +787,52 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>3.90625E-3</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>2.3418426513671878E-2</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>4.2835328727960587E-2</v>
+        <v>4.8828125E-4</v>
       </c>
       <c r="AJ3">
-        <v>6.2157421849406091E-2</v>
+        <v>1.6111373901367191E-2</v>
       </c>
       <c r="AK3">
-        <v>8.5230718205757228E-2</v>
+        <v>3.3618696965277188E-2</v>
       </c>
       <c r="AL3">
-        <v>0.1081688194662704</v>
+        <v>5.1049083550878997E-2</v>
       </c>
       <c r="AM3">
-        <v>0.1309725177897102</v>
+        <v>7.0331070447603228E-2</v>
       </c>
       <c r="AN3">
-        <v>0.15364260069328611</v>
+        <v>8.951890701768328E-2</v>
       </c>
       <c r="AO3">
-        <v>0.18557037207425001</v>
+        <v>0.108613052979511</v>
       </c>
       <c r="AP3">
-        <v>0.20792054567537749</v>
+        <v>0.13141414837220919</v>
+      </c>
+      <c r="AQ3">
+        <v>0.15408164359659079</v>
+      </c>
+      <c r="AR3">
+        <v>0.17661632146614201</v>
+      </c>
+      <c r="AS3">
+        <v>0.1990189602075513</v>
+      </c>
+      <c r="AT3">
+        <v>0.2212903334875852</v>
+      </c>
+      <c r="AU3">
+        <v>0.26926223355073109</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -913,8 +959,23 @@
       <c r="AP4">
         <v>2275797.145823692</v>
       </c>
+      <c r="AQ4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AR4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AS4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AT4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AU4">
+        <v>2275797.145823692</v>
+      </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1012,34 +1073,49 @@
         <v>2275797.145823692</v>
       </c>
       <c r="AG5">
-        <v>2282629.9971868782</v>
+        <v>2275797.145823692</v>
       </c>
       <c r="AH5">
-        <v>2278350.5214072922</v>
+        <v>2275797.145823692</v>
       </c>
       <c r="AI5">
-        <v>2279828.6423239042</v>
+        <v>2275810.0885180579</v>
       </c>
       <c r="AJ5">
-        <v>2289598.2764138998</v>
+        <v>2276714.4819834009</v>
       </c>
       <c r="AK5">
-        <v>2287788.3951594261</v>
+        <v>2275876.221152972</v>
       </c>
       <c r="AL5">
-        <v>2289513.5663511129</v>
+        <v>2279255.820955947</v>
       </c>
       <c r="AM5">
-        <v>2294947.048192922</v>
+        <v>2281233.9960175981</v>
       </c>
       <c r="AN5">
-        <v>2306940.217546335</v>
+        <v>2286464.955164745</v>
       </c>
       <c r="AO5">
-        <v>2275889.773898372</v>
+        <v>2295437.2560704439</v>
       </c>
       <c r="AP5">
-        <v>2308253.2716762219</v>
+        <v>2285247.1323315832</v>
+      </c>
+      <c r="AQ5">
+        <v>2277680.6121181939</v>
+      </c>
+      <c r="AR5">
+        <v>2277668.830514322</v>
+      </c>
+      <c r="AS5">
+        <v>2283439.3684773669</v>
+      </c>
+      <c r="AT5">
+        <v>2300602.4808218582</v>
+      </c>
+      <c r="AU5">
+        <v>2284699.6150477738</v>
       </c>
     </row>
   </sheetData>
@@ -1048,7 +1124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1400,31 +1476,37 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.8125E-3</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>3.12042236328125E-2</v>
+        <v>3.90625E-3</v>
       </c>
       <c r="AH3">
-        <v>5.0583109259605408E-2</v>
+        <v>2.3418426513671878E-2</v>
       </c>
       <c r="AI3">
-        <v>6.9867371421423741E-2</v>
+        <v>4.2835328727960587E-2</v>
       </c>
       <c r="AJ3">
-        <v>9.2895492292001336E-2</v>
+        <v>6.2157421849406091E-2</v>
       </c>
       <c r="AK3">
-        <v>0.1157886827668529</v>
+        <v>8.5230718205757228E-2</v>
       </c>
       <c r="AL3">
-        <v>0.13854773345376589</v>
+        <v>0.1081688194662704</v>
       </c>
       <c r="AM3">
-        <v>0.17248627876520739</v>
+        <v>0.1309725177897102</v>
       </c>
       <c r="AN3">
-        <v>0.21733995518592761</v>
+        <v>0.15364260069328611</v>
+      </c>
+      <c r="AO3">
+        <v>0.18557037207425001</v>
+      </c>
+      <c r="AP3">
+        <v>0.20792054567537749</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.35">
@@ -1548,6 +1630,12 @@
       <c r="AN4">
         <v>2275797.145823692</v>
       </c>
+      <c r="AO4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AP4">
+        <v>2275797.145823692</v>
+      </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -1644,31 +1732,37 @@
         <v>2275797.145823692</v>
       </c>
       <c r="AF5">
-        <v>2329214.5799872158</v>
+        <v>2275797.145823692</v>
       </c>
       <c r="AG5">
-        <v>2293423.0801004879</v>
+        <v>2282629.9971868782</v>
       </c>
       <c r="AH5">
-        <v>2290723.2652849592</v>
+        <v>2278350.5214072922</v>
       </c>
       <c r="AI5">
-        <v>2293493.391445688</v>
+        <v>2279828.6423239042</v>
       </c>
       <c r="AJ5">
-        <v>2288536.7071427568</v>
+        <v>2289598.2764138998</v>
       </c>
       <c r="AK5">
-        <v>2293954.361988917</v>
+        <v>2287788.3951594261</v>
       </c>
       <c r="AL5">
-        <v>2315152.7453481839</v>
+        <v>2289513.5663511129</v>
       </c>
       <c r="AM5">
-        <v>2289411.0046336181</v>
+        <v>2294947.048192922</v>
       </c>
       <c r="AN5">
-        <v>2278085.257495726</v>
+        <v>2306940.217546335</v>
+      </c>
+      <c r="AO5">
+        <v>2275889.773898372</v>
+      </c>
+      <c r="AP5">
+        <v>2308253.2716762219</v>
       </c>
     </row>
   </sheetData>
@@ -1677,7 +1771,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -2023,25 +2117,37 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>3.90625E-3</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>2.3418426513671878E-2</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.6718709170818329E-2</v>
+        <v>7.8125E-3</v>
       </c>
       <c r="AG3">
-        <v>6.9882466734270565E-2</v>
+        <v>3.12042236328125E-2</v>
       </c>
       <c r="AH3">
-        <v>9.2910499155749449E-2</v>
+        <v>5.0583109259605408E-2</v>
       </c>
       <c r="AI3">
-        <v>0.13869670424376801</v>
+        <v>6.9867371421423741E-2</v>
       </c>
       <c r="AJ3">
-        <v>0.1914879602404353</v>
+        <v>9.2895492292001336E-2</v>
+      </c>
+      <c r="AK3">
+        <v>0.1157886827668529</v>
+      </c>
+      <c r="AL3">
+        <v>0.13854773345376589</v>
+      </c>
+      <c r="AM3">
+        <v>0.17248627876520739</v>
+      </c>
+      <c r="AN3">
+        <v>0.21733995518592761</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.35">
@@ -2153,6 +2259,18 @@
       <c r="AJ4">
         <v>2275797.145823692</v>
       </c>
+      <c r="AK4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AL4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AM4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AN4">
+        <v>2275797.145823692</v>
+      </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -2243,25 +2361,37 @@
         <v>2275797.145823692</v>
       </c>
       <c r="AD5">
-        <v>2287764.6268284922</v>
+        <v>2275797.145823692</v>
       </c>
       <c r="AE5">
-        <v>2295149.0413095751</v>
+        <v>2275797.145823692</v>
       </c>
       <c r="AF5">
-        <v>2290911.4555796939</v>
+        <v>2329214.5799872158</v>
       </c>
       <c r="AG5">
-        <v>2294724.9190197159</v>
+        <v>2293423.0801004879</v>
       </c>
       <c r="AH5">
-        <v>2309426.0064811669</v>
+        <v>2290723.2652849592</v>
       </c>
       <c r="AI5">
-        <v>2279108.386843191</v>
+        <v>2293493.391445688</v>
       </c>
       <c r="AJ5">
-        <v>2286741.2782916492</v>
+        <v>2288536.7071427568</v>
+      </c>
+      <c r="AK5">
+        <v>2293954.361988917</v>
+      </c>
+      <c r="AL5">
+        <v>2315152.7453481839</v>
+      </c>
+      <c r="AM5">
+        <v>2289411.0046336181</v>
+      </c>
+      <c r="AN5">
+        <v>2278085.257495726</v>
       </c>
     </row>
   </sheetData>
@@ -2270,7 +2400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -2616,19 +2746,25 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.5625E-2</v>
+        <v>3.90625E-3</v>
       </c>
       <c r="AE3">
-        <v>3.8970947265625E-2</v>
+        <v>2.3418426513671878E-2</v>
       </c>
       <c r="AF3">
-        <v>6.2180101871490479E-2</v>
+        <v>4.6718709170818329E-2</v>
       </c>
       <c r="AG3">
-        <v>9.486708344775252E-2</v>
+        <v>6.9882466734270565E-2</v>
       </c>
       <c r="AH3">
-        <v>0.1635119979965225</v>
+        <v>9.2910499155749449E-2</v>
+      </c>
+      <c r="AI3">
+        <v>0.13869670424376801</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1914879602404353</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.35">
@@ -2734,6 +2870,12 @@
       <c r="AH4">
         <v>2275797.145823692</v>
       </c>
+      <c r="AI4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AJ4">
+        <v>2275797.145823692</v>
+      </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -2824,19 +2966,25 @@
         <v>2275797.145823692</v>
       </c>
       <c r="AD5">
-        <v>2283135.625040188</v>
+        <v>2287764.6268284922</v>
       </c>
       <c r="AE5">
-        <v>2290410.407568926</v>
+        <v>2295149.0413095751</v>
       </c>
       <c r="AF5">
-        <v>2309077.065284126</v>
+        <v>2290911.4555796939</v>
       </c>
       <c r="AG5">
-        <v>2279756.5491609192</v>
+        <v>2294724.9190197159</v>
       </c>
       <c r="AH5">
-        <v>2279089.6994792442</v>
+        <v>2309426.0064811669</v>
+      </c>
+      <c r="AI5">
+        <v>2279108.386843191</v>
+      </c>
+      <c r="AJ5">
+        <v>2286741.2782916492</v>
       </c>
     </row>
   </sheetData>
@@ -2845,7 +2993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -3191,16 +3339,19 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.953125E-2</v>
+        <v>1.5625E-2</v>
       </c>
       <c r="AE3">
-        <v>4.285430908203125E-2</v>
+        <v>3.8970947265625E-2</v>
       </c>
       <c r="AF3">
-        <v>7.763390988111496E-2</v>
+        <v>6.2180101871490479E-2</v>
       </c>
       <c r="AG3">
-        <v>0.13126000876945909</v>
+        <v>9.486708344775252E-2</v>
+      </c>
+      <c r="AH3">
+        <v>0.1635119979965225</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.35">
@@ -3303,6 +3454,9 @@
       <c r="AG4">
         <v>2275797.145823692</v>
       </c>
+      <c r="AH4">
+        <v>2275797.145823692</v>
+      </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -3393,16 +3547,19 @@
         <v>2275797.145823692</v>
       </c>
       <c r="AD5">
-        <v>2291301.542600363</v>
+        <v>2283135.625040188</v>
       </c>
       <c r="AE5">
-        <v>2307556.0323211718</v>
+        <v>2290410.407568926</v>
       </c>
       <c r="AF5">
-        <v>2282466.316228277</v>
+        <v>2309077.065284126</v>
       </c>
       <c r="AG5">
-        <v>2281169.9006730402</v>
+        <v>2279756.5491609192</v>
+      </c>
+      <c r="AH5">
+        <v>2279089.6994792442</v>
       </c>
     </row>
   </sheetData>
@@ -3411,7 +3568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -3765,6 +3922,9 @@
       <c r="AF3">
         <v>7.763390988111496E-2</v>
       </c>
+      <c r="AG3">
+        <v>0.13126000876945909</v>
+      </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -3863,6 +4023,9 @@
       <c r="AF4">
         <v>2275797.145823692</v>
       </c>
+      <c r="AG4">
+        <v>2275797.145823692</v>
+      </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -3953,13 +4116,16 @@
         <v>2275797.145823692</v>
       </c>
       <c r="AD5">
-        <v>2291301.5426006331</v>
+        <v>2291301.542600363</v>
       </c>
       <c r="AE5">
-        <v>2307527.0559320231</v>
+        <v>2307556.0323211718</v>
       </c>
       <c r="AF5">
-        <v>2286793.4218982188</v>
+        <v>2282466.316228277</v>
+      </c>
+      <c r="AG5">
+        <v>2281169.9006730402</v>
       </c>
     </row>
   </sheetData>
@@ -3968,7 +4134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -4510,13 +4676,13 @@
         <v>2275797.145823692</v>
       </c>
       <c r="AD5">
-        <v>2291301.5426004091</v>
+        <v>2291301.5426006331</v>
       </c>
       <c r="AE5">
-        <v>2307567.1693626209</v>
+        <v>2307527.0559320231</v>
       </c>
       <c r="AF5">
-        <v>2286793.4218977429</v>
+        <v>2286793.4218982188</v>
       </c>
     </row>
   </sheetData>
@@ -4525,6 +4691,563 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:AP5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="1">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="1">
+        <v>39</v>
+      </c>
+      <c r="AP1" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0.01</v>
+      </c>
+      <c r="D2">
+        <v>0.02</v>
+      </c>
+      <c r="E2">
+        <v>0.03</v>
+      </c>
+      <c r="F2">
+        <v>0.04</v>
+      </c>
+      <c r="G2">
+        <v>0.05</v>
+      </c>
+      <c r="H2">
+        <v>0.06</v>
+      </c>
+      <c r="I2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J2">
+        <v>0.08</v>
+      </c>
+      <c r="K2">
+        <v>0.09</v>
+      </c>
+      <c r="L2">
+        <v>0.1</v>
+      </c>
+      <c r="M2">
+        <v>0.11</v>
+      </c>
+      <c r="N2">
+        <v>0.12</v>
+      </c>
+      <c r="O2">
+        <v>0.13</v>
+      </c>
+      <c r="P2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>0.15</v>
+      </c>
+      <c r="R2">
+        <v>0.16</v>
+      </c>
+      <c r="S2">
+        <v>0.17</v>
+      </c>
+      <c r="T2">
+        <v>0.18</v>
+      </c>
+      <c r="U2">
+        <v>0.19</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.21</v>
+      </c>
+      <c r="X2">
+        <v>0.22</v>
+      </c>
+      <c r="Y2">
+        <v>0.23</v>
+      </c>
+      <c r="Z2">
+        <v>0.24</v>
+      </c>
+      <c r="AA2">
+        <v>0.25</v>
+      </c>
+      <c r="AB2">
+        <v>0.26</v>
+      </c>
+      <c r="AC2">
+        <v>0.27</v>
+      </c>
+      <c r="AD2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AE2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AF2">
+        <v>0.3</v>
+      </c>
+      <c r="AG2">
+        <v>0.31</v>
+      </c>
+      <c r="AH2">
+        <v>0.32</v>
+      </c>
+      <c r="AI2">
+        <v>0.33</v>
+      </c>
+      <c r="AJ2">
+        <v>0.34</v>
+      </c>
+      <c r="AK2">
+        <v>0.35</v>
+      </c>
+      <c r="AL2">
+        <v>0.36</v>
+      </c>
+      <c r="AM2">
+        <v>0.37</v>
+      </c>
+      <c r="AN2">
+        <v>0.38</v>
+      </c>
+      <c r="AO2">
+        <v>0.39</v>
+      </c>
+      <c r="AP2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>1.953125E-2</v>
+      </c>
+      <c r="AE3">
+        <v>4.285430908203125E-2</v>
+      </c>
+      <c r="AF3">
+        <v>7.763390988111496E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="C4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="D4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="E4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="F4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="G4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="H4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="I4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="J4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="K4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="L4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="M4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="N4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="O4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="P4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="Q4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="R4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="S4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="T4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="U4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="V4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="W4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="X4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="Y4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="Z4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AA4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AB4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AC4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AD4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AE4">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AF4">
+        <v>2275797.145823692</v>
+      </c>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="C5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="D5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="E5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="F5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="G5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="H5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="I5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="J5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="K5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="L5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="M5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="N5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="O5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="P5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="Q5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="R5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="S5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="T5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="U5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="V5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="W5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="X5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="Y5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="Z5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AA5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AB5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AC5">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="AD5">
+        <v>2291301.5426004091</v>
+      </c>
+      <c r="AE5">
+        <v>2307567.1693626209</v>
+      </c>
+      <c r="AF5">
+        <v>2286793.4218977429</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/model/Output_Budget/1. Baseline/Summary.xlsx
+++ b/model/Output_Budget/1. Baseline/Summary.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/Model-1/model/Output_Budget/1. Baseline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_B9E4ED474AC174C29323803AD60FB83079127B7E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3B3F551-4818-4936-9570-126E156CD1A2}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_622DA39E89D7839B17008A1A5C25C9F7AE4BA842" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0A9F4BD-C192-47B8-8DA3-AAA53CE36997}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="100000" sheetId="10" r:id="rId1"/>
-    <sheet name="250000" sheetId="1" r:id="rId2"/>
-    <sheet name="400000" sheetId="9" r:id="rId3"/>
-    <sheet name="750000" sheetId="3" r:id="rId4"/>
-    <sheet name="1000000" sheetId="4" r:id="rId5"/>
+    <sheet name="100000" sheetId="9" r:id="rId1"/>
+    <sheet name="250000" sheetId="2" r:id="rId2"/>
+    <sheet name="400000" sheetId="3" r:id="rId3"/>
+    <sheet name="750000" sheetId="4" r:id="rId4"/>
+    <sheet name="1000000" sheetId="1" r:id="rId5"/>
     <sheet name="1250000" sheetId="5" r:id="rId6"/>
     <sheet name="1500000" sheetId="6" r:id="rId7"/>
     <sheet name="1750000" sheetId="7" r:id="rId8"/>
@@ -402,7 +402,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -837,142 +837,142 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AG4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AH4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AI4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AJ4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AK4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AL4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AM4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AN4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AO4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AP4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AQ4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AR4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AS4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AT4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AU4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
     </row>
     <row r="5" spans="1:47" x14ac:dyDescent="0.35">
@@ -980,142 +980,142 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AG5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AH5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AI5">
-        <v>2275810.0885180579</v>
+        <v>2275912.865534774</v>
       </c>
       <c r="AJ5">
-        <v>2276714.4819834009</v>
+        <v>2276749.7285701949</v>
       </c>
       <c r="AK5">
-        <v>2275876.221152972</v>
+        <v>2276070.6827440732</v>
       </c>
       <c r="AL5">
-        <v>2279255.820955947</v>
+        <v>2279369.9163770722</v>
       </c>
       <c r="AM5">
-        <v>2281233.9960175981</v>
+        <v>2281369.9029168049</v>
       </c>
       <c r="AN5">
-        <v>2286464.955164745</v>
+        <v>2286595.2615608438</v>
       </c>
       <c r="AO5">
-        <v>2295437.2560704439</v>
+        <v>2295468.827332532</v>
       </c>
       <c r="AP5">
-        <v>2285247.1323315832</v>
+        <v>2285408.3366164388</v>
       </c>
       <c r="AQ5">
-        <v>2277680.6121181939</v>
+        <v>2277823.8703487772</v>
       </c>
       <c r="AR5">
-        <v>2277668.830514322</v>
+        <v>2277723.6974346219</v>
       </c>
       <c r="AS5">
-        <v>2283439.3684773669</v>
+        <v>2283676.282248667</v>
       </c>
       <c r="AT5">
-        <v>2300602.4808218582</v>
+        <v>2300652.5064897281</v>
       </c>
       <c r="AU5">
-        <v>2284699.6150477738</v>
+        <v>2284734.761426704</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1514,127 +1514,127 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AG4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AH4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AI4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AJ4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AK4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AL4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AM4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AN4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AO4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AP4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
@@ -1642,127 +1642,127 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AG5">
-        <v>2282629.9971868782</v>
+        <v>2282793.605477035</v>
       </c>
       <c r="AH5">
-        <v>2278350.5214072922</v>
+        <v>2278539.88854999</v>
       </c>
       <c r="AI5">
-        <v>2279828.6423239042</v>
+        <v>2279972.0100517711</v>
       </c>
       <c r="AJ5">
-        <v>2289598.2764138998</v>
+        <v>2289758.793276323</v>
       </c>
       <c r="AK5">
-        <v>2287788.3951594261</v>
+        <v>2288051.5895232512</v>
       </c>
       <c r="AL5">
-        <v>2289513.5663511129</v>
+        <v>2289725.3135765102</v>
       </c>
       <c r="AM5">
-        <v>2294947.048192922</v>
+        <v>2295150.9358702428</v>
       </c>
       <c r="AN5">
-        <v>2306940.217546335</v>
+        <v>2307141.9227375598</v>
       </c>
       <c r="AO5">
-        <v>2275889.773898372</v>
+        <v>2275992.728233349</v>
       </c>
       <c r="AP5">
-        <v>2308253.2716762219</v>
+        <v>2308422.5997130182</v>
       </c>
     </row>
   </sheetData>
@@ -1771,7 +1771,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -2155,121 +2155,121 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AG4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AH4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AI4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AJ4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AK4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AL4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AM4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AN4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
@@ -2277,121 +2277,121 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF5">
-        <v>2329214.5799872158</v>
+        <v>2329418.3755416698</v>
       </c>
       <c r="AG5">
-        <v>2293423.0801004879</v>
+        <v>2293588.1995363389</v>
       </c>
       <c r="AH5">
-        <v>2290723.2652849592</v>
+        <v>2290990.3276657788</v>
       </c>
       <c r="AI5">
-        <v>2293493.391445688</v>
+        <v>2293624.603853025</v>
       </c>
       <c r="AJ5">
-        <v>2288536.7071427568</v>
+        <v>2288667.8911813861</v>
       </c>
       <c r="AK5">
-        <v>2293954.361988917</v>
+        <v>2294172.5266246051</v>
       </c>
       <c r="AL5">
-        <v>2315152.7453481839</v>
+        <v>2315402.6884986102</v>
       </c>
       <c r="AM5">
-        <v>2289411.0046336181</v>
+        <v>2289698.8195712972</v>
       </c>
       <c r="AN5">
-        <v>2278085.257495726</v>
+        <v>2278233.499645181</v>
       </c>
     </row>
   </sheetData>
@@ -2400,7 +2400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -2772,109 +2772,109 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AG4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AH4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AI4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AJ4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
@@ -2882,109 +2882,109 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD5">
-        <v>2287764.6268284922</v>
+        <v>2288108.1047706432</v>
       </c>
       <c r="AE5">
-        <v>2295149.0413095751</v>
+        <v>2295380.6401794101</v>
       </c>
       <c r="AF5">
-        <v>2290911.4555796939</v>
+        <v>2291115.3094753469</v>
       </c>
       <c r="AG5">
-        <v>2294724.9190197159</v>
+        <v>2294778.04124618</v>
       </c>
       <c r="AH5">
-        <v>2309426.0064811669</v>
+        <v>2309491.2487861421</v>
       </c>
       <c r="AI5">
-        <v>2279108.386843191</v>
+        <v>2279274.3923916458</v>
       </c>
       <c r="AJ5">
-        <v>2286741.2782916492</v>
+        <v>2286923.710375479</v>
       </c>
     </row>
   </sheetData>
@@ -2993,7 +2993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -3359,103 +3359,103 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AG4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AH4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
@@ -3463,103 +3463,103 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD5">
-        <v>2283135.625040188</v>
+        <v>2283376.1189919952</v>
       </c>
       <c r="AE5">
-        <v>2290410.407568926</v>
+        <v>2290650.7260758458</v>
       </c>
       <c r="AF5">
-        <v>2309077.065284126</v>
+        <v>2309307.8791784029</v>
       </c>
       <c r="AG5">
-        <v>2279756.5491609192</v>
+        <v>2279930.0601569819</v>
       </c>
       <c r="AH5">
-        <v>2279089.6994792442</v>
+        <v>2279278.165516132</v>
       </c>
     </row>
   </sheetData>
@@ -3931,100 +3931,100 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AG4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
@@ -4032,100 +4032,100 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD5">
-        <v>2291301.542600363</v>
+        <v>2291728.5727346609</v>
       </c>
       <c r="AE5">
-        <v>2307556.0323211718</v>
+        <v>2307832.6962007121</v>
       </c>
       <c r="AF5">
-        <v>2282466.316228277</v>
+        <v>2282696.7102460638</v>
       </c>
       <c r="AG5">
-        <v>2281169.9006730402</v>
+        <v>2281269.4120182502</v>
       </c>
     </row>
   </sheetData>
@@ -4494,97 +4494,97 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
@@ -4592,97 +4592,97 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD5">
-        <v>2291301.5426006331</v>
+        <v>2291728.5727346609</v>
       </c>
       <c r="AE5">
-        <v>2307527.0559320231</v>
+        <v>2307832.6962007112</v>
       </c>
       <c r="AF5">
-        <v>2286793.4218982188</v>
+        <v>2286986.7445619539</v>
       </c>
     </row>
   </sheetData>
@@ -5051,97 +5051,97 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
@@ -5149,97 +5149,97 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD5">
-        <v>2291301.5426004091</v>
+        <v>2291728.5727346619</v>
       </c>
       <c r="AE5">
-        <v>2307567.1693626209</v>
+        <v>2307832.6962007121</v>
       </c>
       <c r="AF5">
-        <v>2286793.4218977429</v>
+        <v>2286986.744561953</v>
       </c>
     </row>
   </sheetData>
@@ -5608,97 +5608,97 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AE4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AF4">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
@@ -5706,97 +5706,97 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="C5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="D5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="E5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="F5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="G5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="H5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="I5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="J5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="K5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="L5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="M5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="N5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="O5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="P5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Q5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="R5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="S5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="T5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="U5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="V5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="W5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="X5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Y5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="Z5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AA5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AB5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AC5">
-        <v>2275797.145823692</v>
+        <v>2275865.281941582</v>
       </c>
       <c r="AD5">
-        <v>2291301.542600072</v>
+        <v>2291728.5727346609</v>
       </c>
       <c r="AE5">
-        <v>2307527.0559314019</v>
+        <v>2307832.6962007121</v>
       </c>
       <c r="AF5">
-        <v>2286793.4218984959</v>
+        <v>2286986.744561953</v>
       </c>
     </row>
   </sheetData>
